--- a/data/availability/projects/misr-italia-properties/club-hill-solare.xlsx
+++ b/data/availability/projects/misr-italia-properties/club-hill-solare.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Dec 2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Dec 2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1059,7 +1059,6 @@
       <c r="G2" t="n">
         <v>115</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1070,7 +1069,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1116,7 +1115,6 @@
       <c r="G3" t="n">
         <v>135</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1127,7 +1125,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1173,7 +1171,6 @@
       <c r="G4" t="n">
         <v>174</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1184,7 +1181,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1230,7 +1227,6 @@
       <c r="G5" t="n">
         <v>174</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1241,7 +1237,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1287,7 +1283,6 @@
       <c r="G6" t="n">
         <v>188</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1298,7 +1293,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1344,7 +1339,6 @@
       <c r="G7" t="n">
         <v>207</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1355,7 +1349,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1401,7 +1395,6 @@
       <c r="G8" t="n">
         <v>109</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1412,7 +1405,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Dec 2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1458,7 +1451,6 @@
       <c r="G9" t="n">
         <v>129</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1469,7 +1461,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Dec 2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
